--- a/Stats Sheet/Round Gaps/All Stars.xlsx
+++ b/Stats Sheet/Round Gaps/All Stars.xlsx
@@ -823,13 +823,13 @@
     <x:t>Kidfo</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>LoafOZ</x:t>
   </x:si>
   <x:si>
     <x:t>MercuryParadox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>Ninetals38</x:t>
@@ -6108,9 +6108,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D243" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M243" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N243" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -6125,12 +6128,9 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D244" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M244" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N244" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
